--- a/week3/manual_gold/603418_友升股份_gold.xlsx
+++ b/week3/manual_gold/603418_友升股份_gold.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,6 +460,16 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>数据来源类型</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>1992年设立，注册资本400万美元，徐泾工业公司出资60%，友升太平洋美国出资40%</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,6 +547,11 @@
           <t>友升太平洋美国出资40%</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -572,6 +592,11 @@
           <t>2020年9月整体变更为股份公司，以经审计净资产折股12000万股</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,6 +633,11 @@
           <t>2020年9月增资，金浦临港、金浦科创、上海骁墨认购1380万元注册资本，每股价格8.3333元</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -644,6 +674,11 @@
           <t>金浦科创认购</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -680,6 +715,11 @@
           <t>上海骁墨认购</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>直接披露</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -714,6 +754,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>2022年12月增资，10家机构认购1100.1333万元注册资本，每股价格33.6323元</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>直接披露</t>
         </is>
       </c>
     </row>
@@ -728,7 +773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,6 +827,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>时点说明</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -830,6 +880,11 @@
           <t>1992年设立，徐泾工业公司出资60%</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -878,6 +933,11 @@
           <t>友升太平洋美国出资40%</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>公司设立后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -926,6 +986,11 @@
           <t>股改后泽升贸易持股74.80%</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -974,6 +1039,11 @@
           <t>达晨创联持股15%</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1022,6 +1092,11 @@
           <t>共青城泽升持股8.50%</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1070,6 +1145,11 @@
           <t>罗世兵持股1.70%</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>整体变更为股份公司后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1120,6 +1200,11 @@
           <t>2020年9月增资后总股本13380万元</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1168,6 +1253,11 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>2022年12月增资后总股本14480.1333万元</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>本次增资完成后的股权结构</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1359,6 +1449,11 @@
           <t>原文证据</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>转让类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1401,6 +1496,7 @@
           <t>翻遍了，发行人层面无股权转让（存在历史股份代持情况，但已解除）</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
